--- a/public/forms/OOO_StudyPlanEx.xlsx
+++ b/public/forms/OOO_StudyPlanEx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TTOKSSAEM\Desktop\문서\학생작성서류\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\withw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A450A572-0292-4414-9087-C45556334B9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A4DF87-9511-4206-9B21-42B894FE3DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{4C914767-CD5A-443D-A8FA-EF6470006C03}"/>
+    <workbookView xWindow="1185" yWindow="60" windowWidth="21420" windowHeight="12015" xr2:uid="{4C914767-CD5A-443D-A8FA-EF6470006C03}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,10 +131,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:40~18:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">14:50~16:37
 </t>
@@ -153,6 +149,10 @@
   </si>
   <si>
     <t>학습계획표(수능시간표용)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00~18:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -289,14 +289,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -623,20 +623,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="3" spans="1:4" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" s="6" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="B4" s="7"/>
@@ -669,7 +669,7 @@
       <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3"/>
@@ -679,7 +679,7 @@
       <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="3"/>
@@ -699,7 +699,7 @@
       <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="3"/>
@@ -709,8 +709,8 @@
       <c r="A11" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>27</v>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -720,7 +720,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
